--- a/grupos/3AEM - Estadisticos 20211.xlsx
+++ b/grupos/3AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -218,6 +218,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAVIER</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -230,7 +239,13 @@
     <t>BERNABE</t>
   </si>
   <si>
-    <t>CORTEZ</t>
+    <t>BUENO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
   </si>
   <si>
     <t>CORTES</t>
@@ -239,9 +254,6 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
     <t>COYOHUA</t>
   </si>
   <si>
@@ -254,6 +266,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -281,9 +296,18 @@
     <t>ROMAN</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>TZANAHUA</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -311,10 +335,10 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>JUAREZ</t>
@@ -323,9 +347,15 @@
     <t>GUZMAN</t>
   </si>
   <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -350,6 +380,9 @@
     <t>YOPIHUA</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -374,7 +407,13 @@
     <t>JOSE ANTONIO</t>
   </si>
   <si>
-    <t>CRISTIAN JAVIER</t>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
   </si>
   <si>
     <t>NEHIZER JAEL</t>
@@ -398,9 +437,15 @@
     <t>ALEXIS MANUEL</t>
   </si>
   <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
     <t>IRVING URIEL</t>
   </si>
   <si>
+    <t>DIEGO ADELFO</t>
+  </si>
+  <si>
     <t>ANDRES NOEL</t>
   </si>
   <si>
@@ -425,6 +470,12 @@
     <t>LUIS ALEJANDRO</t>
   </si>
   <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
     <t>OMAR</t>
   </si>
   <si>
@@ -438,57 +489,6 @@
   </si>
   <si>
     <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>DIEGO ADELFO</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
   </si>
 </sst>
 </file>
@@ -977,10 +977,10 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -995,10 +995,10 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1031,10 +1031,10 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1043,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1054,10 +1054,10 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1066,7 +1066,7 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1108,10 +1108,10 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1120,7 +1120,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1131,7 +1131,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -1143,7 +1143,7 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1185,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1197,7 +1197,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1205,10 +1205,10 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1229,7 +1229,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1259,13 +1259,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1274,7 +1274,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1300,13 +1300,13 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1315,7 +1315,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1342,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1377,13 +1377,13 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1392,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1413,10 +1413,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1436,7 +1436,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -1454,13 +1454,13 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1469,7 +1469,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1490,13 +1490,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1531,13 +1531,13 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1546,7 +1546,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1567,13 +1567,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>6</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1590,10 +1590,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1605,7 +1605,7 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1614,7 +1614,7 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1623,7 +1623,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1644,10 +1644,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1659,7 +1659,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1670,10 +1670,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1682,16 +1682,16 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1721,13 +1721,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1744,13 +1744,13 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>-1</v>
@@ -1759,7 +1759,7 @@
         <v>-1</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1768,7 +1768,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1777,7 +1777,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1798,13 +1798,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>-1</v>
@@ -1813,7 +1813,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1821,13 +1821,13 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1836,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1875,13 +1875,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1890,7 +1890,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1898,13 +1898,13 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1922,7 +1922,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1952,13 +1952,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1967,7 +1967,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1993,13 +1993,13 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2029,13 +2029,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2044,7 +2044,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2055,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -2070,13 +2070,13 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2085,7 +2085,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2106,13 +2106,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2121,7 +2121,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2132,7 +2132,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -2147,13 +2147,13 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2162,7 +2162,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2183,10 +2183,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2198,7 +2198,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2206,13 +2206,13 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -2221,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2260,13 +2260,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2275,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2298,16 +2298,16 @@
         <v>9</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2337,13 +2337,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2378,13 +2378,13 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2414,13 +2414,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2429,7 +2429,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2437,13 +2437,13 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2452,7 +2452,7 @@
         <v>7</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2491,13 +2491,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2506,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2514,10 +2514,10 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2529,16 +2529,16 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2568,13 +2568,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2583,7 +2583,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2606,16 +2606,16 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2648,10 +2648,10 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2660,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2668,13 +2668,13 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2683,7 +2683,7 @@
         <v>7</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2701,7 +2701,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2722,13 +2722,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2737,7 +2737,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2745,13 +2745,13 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -2760,7 +2760,7 @@
         <v>5</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2769,7 +2769,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2778,7 +2778,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2799,13 +2799,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2814,7 +2814,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2822,13 +2822,13 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -2837,16 +2837,16 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2876,13 +2876,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2891,7 +2891,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2899,10 +2899,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -2914,16 +2914,16 @@
         <v>5</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2932,7 +2932,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2953,10 +2953,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -2968,7 +2968,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2979,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>7</v>
@@ -2994,13 +2994,13 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3030,13 +3030,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3077,7 +3077,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3086,7 +3086,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3148,13 +3148,13 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3184,13 +3184,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>7</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3199,7 +3199,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3225,13 +3225,13 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3240,7 +3240,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3264,10 +3264,10 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3284,13 +3284,13 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3299,7 +3299,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3308,7 +3308,7 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3338,13 +3338,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>7</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3353,7 +3353,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3361,13 +3361,13 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -3376,7 +3376,7 @@
         <v>5</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3394,7 +3394,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3415,13 +3415,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>5</v>
@@ -3430,7 +3430,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3441,10 +3441,10 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3462,7 +3462,7 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3471,7 +3471,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3495,10 +3495,10 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3507,7 +3507,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3515,13 +3515,13 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>5</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3539,7 +3539,7 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3548,7 +3548,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3569,13 +3569,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -3584,7 +3584,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3595,7 +3595,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>8</v>
@@ -3613,10 +3613,10 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3625,7 +3625,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3649,10 +3649,10 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -3661,7 +3661,7 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3669,13 +3669,13 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -3684,16 +3684,16 @@
         <v>5</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3702,7 +3702,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3723,13 +3723,13 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -3738,7 +3738,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3803,94 +3803,94 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>66.67</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>36</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>38.89</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>61.11</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="G4">
-        <v>47.22</v>
+        <v>44.44</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3899,25 +3899,25 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="G5">
-        <v>47.22</v>
+        <v>41.67</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3931,25 +3931,25 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>66.67</v>
+      </c>
+      <c r="G6">
+        <v>33.33</v>
+      </c>
+      <c r="H6">
+        <v>6.4</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>52.78</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>6.8</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>47.22</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3963,25 +3963,25 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>80.56</v>
+      </c>
+      <c r="G7">
+        <v>19.44</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>55.56</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7.6</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>44.44</v>
       </c>
     </row>
   </sheetData>
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4020,19 +4020,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920001</v>
+        <v>20330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -4040,1602 +4040,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920001</v>
+        <v>20330051920005</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920001</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920002</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920002</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920361</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920361</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920003</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920003</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920003</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920005</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920005</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920005</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920005</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920005</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920005</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920008</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920008</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920008</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920362</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920362</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920362</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920009</v>
-      </c>
-      <c r="B24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920010</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920010</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920010</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920010</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920011</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920012</v>
-      </c>
-      <c r="B30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920013</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920013</v>
-      </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920013</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920013</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920014</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920016</v>
-      </c>
-      <c r="B36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920016</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920016</v>
-      </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920016</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920363</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920363</v>
-      </c>
-      <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920363</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920363</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920021</v>
-      </c>
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920021</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920021</v>
-      </c>
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920023</v>
-      </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920024</v>
-      </c>
-      <c r="B48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920024</v>
-      </c>
-      <c r="B49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" t="s">
-        <v>130</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920024</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920024</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D51" t="s">
-        <v>130</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920025</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" t="s">
-        <v>131</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920025</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920025</v>
-      </c>
-      <c r="B54" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D54" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920025</v>
-      </c>
-      <c r="B55" t="s">
-        <v>83</v>
-      </c>
-      <c r="C55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D55" t="s">
-        <v>131</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920026</v>
-      </c>
-      <c r="B56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" t="s">
-        <v>132</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920026</v>
-      </c>
-      <c r="B57" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" t="s">
-        <v>132</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920026</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
-        <v>132</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920026</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" t="s">
-        <v>107</v>
-      </c>
-      <c r="D59" t="s">
-        <v>132</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920060</v>
-      </c>
-      <c r="B60" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" t="s">
-        <v>108</v>
-      </c>
-      <c r="D60" t="s">
-        <v>133</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920060</v>
-      </c>
-      <c r="B61" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61" t="s">
-        <v>133</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920060</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" t="s">
-        <v>108</v>
-      </c>
-      <c r="D62" t="s">
-        <v>133</v>
-      </c>
-      <c r="E62" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920027</v>
-      </c>
-      <c r="B63" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" t="s">
-        <v>134</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920031</v>
-      </c>
-      <c r="B64" t="s">
-        <v>87</v>
-      </c>
-      <c r="C64" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64" t="s">
-        <v>135</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920031</v>
-      </c>
-      <c r="B65" t="s">
-        <v>87</v>
-      </c>
-      <c r="C65" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920031</v>
-      </c>
-      <c r="B66" t="s">
-        <v>87</v>
-      </c>
-      <c r="C66" t="s">
-        <v>109</v>
-      </c>
-      <c r="D66" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920031</v>
-      </c>
-      <c r="B67" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67" t="s">
-        <v>135</v>
-      </c>
-      <c r="E67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920033</v>
-      </c>
-      <c r="B68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D68" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920033</v>
-      </c>
-      <c r="B69" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" t="s">
-        <v>88</v>
-      </c>
-      <c r="D69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920033</v>
-      </c>
-      <c r="B70" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" t="s">
-        <v>88</v>
-      </c>
-      <c r="D70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920034</v>
-      </c>
-      <c r="B71" t="s">
-        <v>89</v>
-      </c>
-      <c r="C71" t="s">
-        <v>110</v>
-      </c>
-      <c r="D71" t="s">
-        <v>137</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920034</v>
-      </c>
-      <c r="B72" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" t="s">
-        <v>137</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920034</v>
-      </c>
-      <c r="B73" t="s">
-        <v>89</v>
-      </c>
-      <c r="C73" t="s">
-        <v>110</v>
-      </c>
-      <c r="D73" t="s">
-        <v>137</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920035</v>
-      </c>
-      <c r="B74" t="s">
-        <v>90</v>
-      </c>
-      <c r="C74" t="s">
-        <v>111</v>
-      </c>
-      <c r="D74" t="s">
-        <v>138</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920035</v>
-      </c>
-      <c r="B75" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" t="s">
-        <v>111</v>
-      </c>
-      <c r="D75" t="s">
-        <v>138</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920035</v>
-      </c>
-      <c r="B76" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" t="s">
-        <v>138</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920035</v>
-      </c>
-      <c r="B77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77" t="s">
-        <v>111</v>
-      </c>
-      <c r="D77" t="s">
-        <v>138</v>
-      </c>
-      <c r="E77" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920036</v>
-      </c>
-      <c r="B78" t="s">
-        <v>91</v>
-      </c>
-      <c r="C78" t="s">
-        <v>112</v>
-      </c>
-      <c r="D78" t="s">
-        <v>117</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920037</v>
-      </c>
-      <c r="B79" t="s">
-        <v>92</v>
-      </c>
-      <c r="C79" t="s">
-        <v>113</v>
-      </c>
-      <c r="D79" t="s">
-        <v>139</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920037</v>
-      </c>
-      <c r="B80" t="s">
-        <v>92</v>
-      </c>
-      <c r="C80" t="s">
-        <v>113</v>
-      </c>
-      <c r="D80" t="s">
-        <v>139</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920037</v>
-      </c>
-      <c r="B81" t="s">
-        <v>92</v>
-      </c>
-      <c r="C81" t="s">
-        <v>113</v>
-      </c>
-      <c r="D81" t="s">
-        <v>139</v>
-      </c>
-      <c r="E81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920037</v>
-      </c>
-      <c r="B82" t="s">
-        <v>92</v>
-      </c>
-      <c r="C82" t="s">
-        <v>113</v>
-      </c>
-      <c r="D82" t="s">
-        <v>139</v>
-      </c>
-      <c r="E82" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5674,441 +4094,441 @@
         <v>20330051920005</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920010</v>
+        <v>20330051920001</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920013</v>
+        <v>20330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920016</v>
+        <v>20330051920361</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920363</v>
+        <v>20330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920024</v>
+        <v>20330051920004</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
         <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920025</v>
+        <v>20330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
         <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920026</v>
+        <v>20330051920007</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920031</v>
+        <v>20330051920008</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920035</v>
+        <v>20330051920362</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920037</v>
+        <v>20330051920009</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920001</v>
+        <v>20330051920010</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920003</v>
+        <v>20330051920011</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920008</v>
+        <v>20330051920012</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920362</v>
+        <v>20330051920013</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920021</v>
+        <v>20330051920014</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920060</v>
+        <v>20330051920015</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920033</v>
+        <v>20330051920016</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920034</v>
+        <v>20330051920017</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920002</v>
+        <v>20330051920363</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920361</v>
+        <v>20330051920021</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920009</v>
+        <v>20330051920023</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920011</v>
+        <v>20330051920024</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920012</v>
+        <v>20330051920025</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920014</v>
+        <v>20330051920026</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920023</v>
+        <v>20330051920060</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6116,47 +4536,47 @@
         <v>20330051920027</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920036</v>
+        <v>20330051920028</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920004</v>
+        <v>20330051920029</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6164,16 +4584,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920006</v>
+        <v>20330051920031</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6181,16 +4601,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920007</v>
+        <v>20330051920032</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6198,13 +4618,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920015</v>
+        <v>20330051920033</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -6215,13 +4635,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920017</v>
+        <v>20330051920034</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -6232,13 +4652,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920028</v>
+        <v>20330051920035</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -6249,16 +4669,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920029</v>
+        <v>20330051920036</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6266,16 +4686,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920032</v>
+        <v>20330051920037</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6288,7 +4708,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6320,114 +4740,114 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920060</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920002</v>
+        <v>20330051920060</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920361</v>
+        <v>20330051920029</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920361</v>
+        <v>20330051920029</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920029</v>
+        <v>20330051920033</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6435,22 +4855,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920029</v>
+        <v>20330051920033</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6458,163 +4878,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920009</v>
+        <v>20330051920002</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920011</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920012</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920014</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920023</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920027</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920036</v>
-      </c>
-      <c r="B14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3AEM - Estadisticos 20211.xlsx
+++ b/grupos/3AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -191,18 +191,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -218,196 +218,196 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BUENO</t>
+  </si>
+  <si>
     <t>CORTEZ</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
     <t>CRISTIAN JAVIER</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
   </si>
   <si>
     <t>MISAEL</t>
@@ -1001,10 +1001,10 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1078,10 +1078,10 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1114,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1155,10 +1155,10 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1194,7 +1194,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1232,10 +1232,10 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -1268,10 +1268,10 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1309,10 +1309,10 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1345,10 +1345,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1386,10 +1386,10 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1422,10 +1422,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1463,10 +1463,10 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1499,10 +1499,10 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1540,10 +1540,10 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1576,10 +1576,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1617,10 +1617,10 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1653,7 +1653,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1694,10 +1694,10 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1753,10 +1753,10 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1771,10 +1771,10 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1807,10 +1807,10 @@
         <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1848,10 +1848,10 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1884,7 +1884,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1925,10 +1925,10 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2002,10 +2002,10 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2038,10 +2038,10 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2079,10 +2079,10 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2115,7 +2115,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2156,10 +2156,10 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2192,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2233,10 +2233,10 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2269,7 +2269,7 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2310,10 +2310,10 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2387,10 +2387,10 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2423,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2464,10 +2464,10 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2500,10 +2500,10 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2541,10 +2541,10 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2577,10 +2577,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2618,10 +2618,10 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -2654,10 +2654,10 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2695,10 +2695,10 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -2731,10 +2731,10 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2772,10 +2772,10 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2808,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2849,10 +2849,10 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -2885,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2926,10 +2926,10 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -2962,10 +2962,10 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3003,10 +3003,10 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3039,10 +3039,10 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3080,10 +3080,10 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -3116,10 +3116,10 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3157,10 +3157,10 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>7</v>
@@ -3193,10 +3193,10 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3234,10 +3234,10 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3270,7 +3270,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3311,10 +3311,10 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -3347,10 +3347,10 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3388,10 +3388,10 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3424,7 +3424,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3465,10 +3465,10 @@
         <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -3501,10 +3501,10 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3542,10 +3542,10 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>6</v>
@@ -3578,10 +3578,10 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3619,10 +3619,10 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
         <v>8</v>
@@ -3655,7 +3655,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3696,10 +3696,10 @@
         <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -3732,7 +3732,7 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>5</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3803,83 +3803,83 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="G2">
-        <v>47.22</v>
+        <v>44.44</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>36</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="G3">
-        <v>47.22</v>
+        <v>41.67</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>55.56</v>
+        <v>66.67</v>
       </c>
       <c r="G4">
-        <v>44.44</v>
+        <v>33.33</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3890,28 +3890,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>58.33</v>
+        <v>69.44</v>
       </c>
       <c r="G5">
-        <v>41.67</v>
+        <v>30.56</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3922,28 +3922,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>66.67</v>
+        <v>80.56</v>
       </c>
       <c r="G6">
-        <v>33.33</v>
+        <v>19.44</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3954,28 +3954,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>80.56</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>19.44</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4016,46 +4016,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920005</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920005</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4091,30 +4051,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920005</v>
+        <v>20330051920001</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920001</v>
+        <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
         <v>125</v>
@@ -4125,13 +4085,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920002</v>
+        <v>20330051920361</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
         <v>126</v>
@@ -4142,13 +4102,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920361</v>
+        <v>20330051920003</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>127</v>
@@ -4159,13 +4119,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920003</v>
+        <v>20330051920004</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>128</v>
@@ -4176,13 +4136,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920004</v>
+        <v>20330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>129</v>
@@ -4196,10 +4156,10 @@
         <v>20330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>130</v>
@@ -4213,10 +4173,10 @@
         <v>20330051920007</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
@@ -4230,10 +4190,10 @@
         <v>20330051920008</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>132</v>
@@ -4247,10 +4207,10 @@
         <v>20330051920362</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -4264,10 +4224,10 @@
         <v>20330051920009</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
         <v>134</v>
@@ -4281,13 +4241,13 @@
         <v>20330051920010</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4298,10 +4258,10 @@
         <v>20330051920011</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4315,10 +4275,10 @@
         <v>20330051920012</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4332,10 +4292,10 @@
         <v>20330051920013</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4349,10 +4309,10 @@
         <v>20330051920014</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4366,10 +4326,10 @@
         <v>20330051920015</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4383,10 +4343,10 @@
         <v>20330051920016</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4400,10 +4360,10 @@
         <v>20330051920017</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4417,10 +4377,10 @@
         <v>20330051920363</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4434,10 +4394,10 @@
         <v>20330051920021</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4451,10 +4411,10 @@
         <v>20330051920023</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4468,10 +4428,10 @@
         <v>20330051920024</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4485,10 +4445,10 @@
         <v>20330051920025</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4502,10 +4462,10 @@
         <v>20330051920026</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4519,10 +4479,10 @@
         <v>20330051920060</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4536,10 +4496,10 @@
         <v>20330051920027</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4553,10 +4513,10 @@
         <v>20330051920028</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4570,10 +4530,10 @@
         <v>20330051920029</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -4587,10 +4547,10 @@
         <v>20330051920031</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
         <v>152</v>
@@ -4604,10 +4564,10 @@
         <v>20330051920032</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
         <v>130</v>
@@ -4621,10 +4581,10 @@
         <v>20330051920033</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -4638,10 +4598,10 @@
         <v>20330051920034</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -4655,10 +4615,10 @@
         <v>20330051920035</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -4672,13 +4632,13 @@
         <v>20330051920036</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -4689,10 +4649,10 @@
         <v>20330051920037</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
         <v>156</v>
@@ -4708,7 +4668,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4740,22 +4700,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920060</v>
+        <v>20330051920003</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4763,19 +4723,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920060</v>
+        <v>20330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -4786,22 +4746,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920029</v>
+        <v>20330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4809,19 +4769,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920029</v>
+        <v>20330051920021</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>57</v>
@@ -4832,70 +4792,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920033</v>
+        <v>20330051920035</v>
       </c>
       <c r="B6" t="s">
         <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920033</v>
-      </c>
-      <c r="B7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920002</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20211.xlsx
+++ b/grupos/3AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -197,10 +197,10 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
@@ -2224,7 +2224,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2260,7 +2260,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -2455,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2491,7 +2491,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2686,7 +2686,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2722,7 +2722,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>5</v>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2799,7 +2799,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3867,19 +3867,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>69.44</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>30.56</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3899,19 +3899,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="G5">
-        <v>30.56</v>
+        <v>22.22</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -4668,7 +4668,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4715,7 +4715,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4746,22 +4746,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920002</v>
+        <v>20330051920363</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4769,16 +4769,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920021</v>
+        <v>20330051920363</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4792,16 +4792,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920035</v>
+        <v>20330051920025</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4810,6 +4810,98 @@
         <v>58</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920002</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920021</v>
+      </c>
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920035</v>
+      </c>
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20211.xlsx
+++ b/grupos/3AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -197,13 +197,13 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -1010,31 +1010,31 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1043,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1069,10 +1069,10 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -1087,25 +1087,25 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -1146,10 +1146,10 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -1164,37 +1164,37 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>6</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1223,10 +1223,10 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -1241,40 +1241,40 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>6</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1318,22 +1318,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1342,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1395,25 +1395,25 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1472,22 +1472,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1496,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1549,22 +1549,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1608,10 +1608,10 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1626,22 +1626,22 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1650,7 +1650,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1688,7 +1688,7 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1703,31 +1703,31 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1762,10 +1762,10 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1780,22 +1780,22 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1804,7 +1804,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1839,10 +1839,10 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1857,22 +1857,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1916,10 +1916,10 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1934,22 +1934,22 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1961,10 +1961,10 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2011,22 +2011,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2035,7 +2035,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2073,7 +2073,7 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -2088,25 +2088,25 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>8</v>
@@ -2165,31 +2165,31 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2227,7 +2227,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -2242,22 +2242,22 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2269,13 +2269,13 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2304,7 +2304,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2319,22 +2319,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2396,22 +2396,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2458,7 +2458,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -2473,28 +2473,28 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>6</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2503,7 +2503,7 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2550,25 +2550,25 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2580,10 +2580,10 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2609,7 +2609,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -2627,22 +2627,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2689,7 +2689,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2704,37 +2704,37 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2766,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2781,25 +2781,25 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2840,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2858,22 +2858,22 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2882,7 +2882,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2917,7 +2917,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2935,40 +2935,40 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>6</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3012,31 +3012,31 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3071,10 +3071,10 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -3089,37 +3089,37 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>7</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3151,7 +3151,7 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>9</v>
@@ -3166,31 +3166,31 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3243,22 +3243,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3302,10 +3302,10 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -3320,28 +3320,28 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3350,7 +3350,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3379,10 +3379,10 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>6</v>
@@ -3397,22 +3397,22 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>5</v>
@@ -3421,13 +3421,13 @@
         <v>5</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3456,10 +3456,10 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -3474,37 +3474,37 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>5</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3533,10 +3533,10 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -3551,40 +3551,40 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>5</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>8</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3610,7 +3610,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>7</v>
@@ -3628,28 +3628,28 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -3687,7 +3687,7 @@
         <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -3705,22 +3705,22 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -3729,13 +3729,13 @@
         <v>5</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>8</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3803,19 +3803,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>55.56</v>
+        <v>58.33</v>
       </c>
       <c r="G2">
-        <v>44.44</v>
+        <v>41.67</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3835,19 +3835,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>58.33</v>
+        <v>61.11</v>
       </c>
       <c r="G3">
-        <v>41.67</v>
+        <v>38.89</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3867,19 +3867,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>69.44</v>
+        <v>66.67</v>
       </c>
       <c r="G4">
-        <v>30.56</v>
+        <v>33.33</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3899,19 +3899,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>77.78</v>
+        <v>66.67</v>
       </c>
       <c r="G5">
-        <v>22.22</v>
+        <v>33.33</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3943,7 +3943,7 @@
         <v>19.44</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4668,7 +4668,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4700,22 +4700,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920003</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920003</v>
+        <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4746,22 +4746,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920363</v>
+        <v>20330051920025</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4769,16 +4769,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920363</v>
+        <v>20330051920025</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4792,22 +4792,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920025</v>
+        <v>20330051920034</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4815,16 +4815,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920025</v>
+        <v>20330051920034</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4833,75 +4833,6 @@
         <v>57</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920002</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920021</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920035</v>
-      </c>
-      <c r="B10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
